--- a/data/breaker_canvas_layout.xlsx
+++ b/data/breaker_canvas_layout.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,25 +497,25 @@
         <v>1.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>41.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>9152</v>
+        <v>14872</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="H2" t="n">
-        <v>120</v>
+        <v>27.58</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>28.35</v>
       </c>
       <c r="J2" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="K2" t="n">
         <v>120</v>
@@ -548,13 +548,13 @@
         <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>360</v>
+        <v>322.36</v>
       </c>
       <c r="I3" t="n">
-        <v>222</v>
+        <v>173.83</v>
       </c>
       <c r="J3" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="K3" t="n">
         <v>120</v>
@@ -575,25 +575,25 @@
         <v>1.25</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>31.2</v>
+        <v>57.2</v>
       </c>
       <c r="F4" t="n">
-        <v>6864</v>
+        <v>12584</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
-        <v>66</v>
+        <v>28.36</v>
       </c>
       <c r="I4" t="n">
-        <v>223</v>
+        <v>174.83</v>
       </c>
       <c r="J4" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="K4" t="n">
         <v>120</v>
@@ -602,7 +602,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCCB-04</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,25 +614,25 @@
         <v>1.25</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>20.8</v>
+        <v>46.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4576</v>
+        <v>10296</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>55</v>
+        <v>32.06</v>
       </c>
       <c r="I5" t="n">
-        <v>455</v>
+        <v>421.53</v>
       </c>
       <c r="J5" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="K5" t="n">
         <v>120</v>
@@ -665,15 +665,171 @@
         <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>652</v>
+        <v>614.36</v>
       </c>
       <c r="I6" t="n">
-        <v>223</v>
+        <v>174.83</v>
       </c>
       <c r="J6" t="n">
         <v>280</v>
       </c>
       <c r="K6" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CP02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MCCB-03</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>589.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>425.48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>220</v>
+      </c>
+      <c r="K7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MCCB-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MAIN-MCCB</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>931.73</v>
+      </c>
+      <c r="I8" t="n">
+        <v>175.71</v>
+      </c>
+      <c r="J8" t="n">
+        <v>280</v>
+      </c>
+      <c r="K8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MCCB-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MAIN-MCCB</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1256.73</v>
+      </c>
+      <c r="I9" t="n">
+        <v>175.71</v>
+      </c>
+      <c r="J9" t="n">
+        <v>280</v>
+      </c>
+      <c r="K9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MCCB-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MAIN-MCCB</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1576.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>179.46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>280</v>
+      </c>
+      <c r="K10" t="n">
         <v>120</v>
       </c>
     </row>
@@ -688,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,16 +941,16 @@
         <v>1144</v>
       </c>
       <c r="I2" t="n">
-        <v>492</v>
+        <v>371.05</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>332.73</v>
       </c>
       <c r="K2" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -829,16 +985,16 @@
         <v>1144</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>22.46</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>326.83</v>
       </c>
       <c r="K3" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L3" t="n">
-        <v>68</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="4">
@@ -873,22 +1029,22 @@
         <v>1144</v>
       </c>
       <c r="I4" t="n">
-        <v>281</v>
+        <v>199.25</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>334.36</v>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L4" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCCB-04</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,22 +1073,22 @@
         <v>1144</v>
       </c>
       <c r="I5" t="n">
-        <v>44</v>
+        <v>21.06</v>
       </c>
       <c r="J5" t="n">
-        <v>606</v>
+        <v>572.53</v>
       </c>
       <c r="K5" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L5" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MCCB-04</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -961,22 +1117,22 @@
         <v>1144</v>
       </c>
       <c r="I6" t="n">
-        <v>259</v>
+        <v>203.02</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
+        <v>574.53</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MCCB-04</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1005,22 +1161,22 @@
         <v>1144</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>21.06</v>
       </c>
       <c r="J7" t="n">
-        <v>689</v>
+        <v>655.53</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L7" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MCCB-04</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1049,22 +1205,22 @@
         <v>1144</v>
       </c>
       <c r="I8" t="n">
-        <v>260</v>
+        <v>201.41</v>
       </c>
       <c r="J8" t="n">
-        <v>689</v>
+        <v>655.53</v>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L8" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MCCB-03</t>
+          <t>CP01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1093,15 +1249,235 @@
         <v>1144</v>
       </c>
       <c r="I9" t="n">
-        <v>699</v>
+        <v>22.06</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>737.53</v>
       </c>
       <c r="K9" t="n">
+        <v>160</v>
+      </c>
+      <c r="L9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CP01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MTR-001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Main Motor</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I10" t="n">
+        <v>201.74</v>
+      </c>
+      <c r="J10" t="n">
+        <v>735.64</v>
+      </c>
+      <c r="K10" t="n">
+        <v>160</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CP01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MTR-001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Main Motor</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>897.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>160</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CP01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MTR-001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Main Motor</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I12" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>827.4299999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>160</v>
+      </c>
+      <c r="L12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CP01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MTR-001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Main Motor</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="J13" t="n">
+        <v>815.99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>160</v>
+      </c>
+      <c r="L13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MCCB-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MTR-001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Main Motor</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1144</v>
+      </c>
+      <c r="I14" t="n">
+        <v>613.99</v>
+      </c>
+      <c r="J14" t="n">
+        <v>318.03</v>
+      </c>
+      <c r="K14" t="n">
         <v>200</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L14" t="n">
         <v>68</v>
       </c>
     </row>
